--- a/artfynd/A 23818-2025 artfynd.xlsx
+++ b/artfynd/A 23818-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113727814</v>
+        <v>112266009</v>
       </c>
       <c r="B2" t="n">
-        <v>56478</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,39 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>2412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Källmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Philonotis fontana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Kall, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411151</v>
+        <v>411114</v>
       </c>
       <c r="R2" t="n">
-        <v>7040085</v>
+        <v>7040155</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,9 +758,15 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>källa</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -788,7 +778,331 @@
           <t>Linda Johannesson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>UU_kurs_lavsvampmoss_ht23</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>110740751</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96154</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2697</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nordlig tuffmossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Palustriella decipiens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(De Not.) Ochyra</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>411113</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7040152</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-06-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Linda Johannesson, Jesper Wadstein</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>112266008</v>
+      </c>
+      <c r="B4" t="n">
+        <v>96154</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2697</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Nordlig tuffmossa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Palustriella decipiens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(De Not.) Ochyra</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>411114</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7040155</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2023-09-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>källa</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>UU_kurs_lavsvampmoss_ht23</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>113727814</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Kall, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>411151</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7040085</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Kall</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-12-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Linda Johannesson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
